--- a/GATEWAY/A1#111#AISMXX/AISM/Rehab-MS/1.8/accreditamento-checklist_V8.3.0.xlsx
+++ b/GATEWAY/A1#111#AISMXX/AISM/Rehab-MS/1.8/accreditamento-checklist_V8.3.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gaetano.paterno\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{105F9BCD-C7E2-4E4B-B0F8-DD06BEF1FCD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14C1AD8A-E3BE-4F27-A94B-B21A7F4EA211}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="1620" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1547" uniqueCount="633">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1550" uniqueCount="635">
   <si>
     <t>COME VALORIZZARE LA CHECKLIST (tab TestCases)</t>
   </si>
@@ -2086,6 +2086,18 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 6" riportata nei documenti "casi di test TPI" e "CDA2_Tessera_Portatore_Impianto_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento. </t>
   </si>
   <si>
+    <t>subject_application_id: Rehab-MS</t>
+  </si>
+  <si>
+    <t>subject_application_vendor: AISM</t>
+  </si>
+  <si>
+    <t>subject_application_version: 1.8</t>
+  </si>
+  <si>
+    <t>AISM</t>
+  </si>
+  <si>
     <t>2026-03-12T16:02:00Z</t>
   </si>
   <si>
@@ -2275,76 +2287,70 @@
     <t>title:"Campo token JWT non valido.","detail":"Il campo purpose_of_use non è valorizzato","status":403</t>
   </si>
   <si>
+    <t>title:"Campo token JWT non valido.","detail":"Il campo action_id non è corretto","status":403</t>
+  </si>
+  <si>
+    <t>TIMEOUT</t>
+  </si>
+  <si>
+    <t>[ERRORE-44| Il codice fiscale 'pznttf80a50d548v' cittadino ed operatore deve essere costituito da 16 cifre [A-Z0-9]{16}],[ERRORE-44| Il codice fiscale 'mrrssi87d52s969a' cittadino ed operatore deve essere costituito da 16 cifre [A-Z0-9]{16}],[ERRORE-44| Il codice fiscale 'mrrssi87d52s969a' cittadino ed operatore deve essere costituito da 16 cifre [A-Z0-9]{16}]</t>
+  </si>
+  <si>
+    <t>[ERRORE-11| L'elemento ClinicalDocument/recordTarget/patientRole/addr DEVE riportare i sotto-elementi 'country', 'city' e 'streetAddressLine' ]</t>
+  </si>
+  <si>
+    <t>[ERRORE-14| L'elemento ClinicalDocument/recordTaget/patientRole/patient/name DEVE riportare gli elementi 'given' e 'family']</t>
+  </si>
+  <si>
+    <t>Almeno uno dei seguenti vocaboli non è censito: [CodeSystem: 2.16.840.1.113883.5.1 v2.1.0, Codes: VALORE_ERRATO]</t>
+  </si>
+  <si>
+    <t>ERROR: -1,-1 cvc-complex-type.2.4.a: Invalid content was found starting with element '{"urn:hl7-org:v3":priorityCode}'. One of '{"urn:hl7-org:v3":realmCode, "urn:hl7-org:v3":typeId, "urn:hl7-org:v3":templateId, "urn:hl7-org:v3":id}' is expected.</t>
+  </si>
+  <si>
+    <t>ERROR: -1,-1 cvc-complex-type.2.4.a: Invalid content was found starting with element '{"urn:hl7-org:v3":effectiveTime}'. One of '{"urn:hl7-org:v3":realmCode, "urn:hl7-org:v3":typeId, "urn:hl7-org:v3":templateId, "urn:hl7-org:v3":id, "urn:hl7-org:v3":code}' is expected.</t>
+  </si>
+  <si>
+    <t>[ERRORE-b4| Sezione Referto: la sezione DEVE essere presente],[ERRORE-b5| Sezione Referto: la sezione DEVE contenere un elemento 'text']</t>
+  </si>
+  <si>
+    <t>[ERRORE-b6| Sezione Quesito Diagnostico: la sezione DEVE contenere un elemento 'text']</t>
+  </si>
+  <si>
+    <t>ERROR: -1,-1 cvc-complex-type.2.4.b: The content of element 'entry' is not complete. One of '{"urn:hl7-org:v3":realmCode, "urn:hl7-org:v3":typeId, "urn:hl7-org:v3":templateId, "urn:hl7-org:v3":act, "urn:hl7-org:v3":encounter, "urn:hl7-org:v3":observation, "urn:hl7-org:v3":observationMedia, "urn:hl7-org:v3":organizer, "urn:hl7-org:v3":procedure, "urn:hl7-org:v3":regionOfInterest, "urn:hl7-org:v3":substanceAdministration, "urn:hl7-org:v3":supply}' is expected.</t>
+  </si>
+  <si>
+    <t>[ERRORE-b26| Sezione Storia Clinica: l'elemento entry/observation/effectiveTime deve essere presente e deve avere l'elemento 'low' valorizzato]</t>
+  </si>
+  <si>
+    <t>[ERRORE-b36| Sezione Storia Clinica: l'elemento entry/organizer/subject/relatedSubject deve avere l'attributo @classCode='PRS' e deve contenere l'elemento 'code']</t>
+  </si>
+  <si>
+    <t>[ERRORE-b53| Sotto-sezione Allergie: l'elemento entry/act/entryRelationship/observation/effectiveTime deve essere presente e deve avere l'elemento 'low' valorizzato ]</t>
+  </si>
+  <si>
+    <t>[ERRORE-b57| Sotto-sezione Allergie: entry/act/entryRelationship/observation deve contenere almeno un elemento 'participant']</t>
+  </si>
+  <si>
+    <t>[ERRORE-b22| Sezione Quesito Diagnostico: l'elemento entry/observation/value DEVE avere attributo @codeSystem valorizzato con l'OID del sistema di codifica ICD-9-CM ]</t>
+  </si>
+  <si>
+    <t>[ERRORE-30| L'elemento ClinicalDocument/legalAuthenticator/signatureCode deve essere valorizzato con il codice "S" ]</t>
+  </si>
+  <si>
+    <t>[ERRORE-b41| Sezione Storia Clinica: l'elemento entry/organizer/component/observation/value deve essere presente e valorizzato secondo il @codeSystem='2.16.840.1.113883.6.103' ]</t>
+  </si>
+  <si>
+    <t>ERROR: -1,-1 cvc-complex-type.2.4.a: Invalid content was found starting with element '{"urn:hl7-org:v3":languageCode}'. One of '{"urn:hl7-org:v3":confidentialityCode}' is expected.</t>
+  </si>
+  <si>
+    <t>Almeno uno dei seguenti vocaboli non è censito: [CodeSystem: 2.16.840.1.113883.5.7 v2.1.0, Codes: VALORE_ERRATO]</t>
+  </si>
+  <si>
     <t>L'errore viene gestito in maniera trasparente all’operatore, con la notifica di un messaggio di errore. In caso di retry del fallimento, l'errore viene gestito dall’operatore effettuando un nuovo tentativo di invio.</t>
   </si>
   <si>
-    <t>title:"Campo token JWT non valido.","detail":"Il campo action_id non è corretto","status":403</t>
-  </si>
-  <si>
-    <t>TIMEOUT</t>
-  </si>
-  <si>
-    <t>[ERRORE-44| Il codice fiscale 'pznttf80a50d548v' cittadino ed operatore deve essere costituito da 16 cifre [A-Z0-9]{16}],[ERRORE-44| Il codice fiscale 'mrrssi87d52s969a' cittadino ed operatore deve essere costituito da 16 cifre [A-Z0-9]{16}],[ERRORE-44| Il codice fiscale 'mrrssi87d52s969a' cittadino ed operatore deve essere costituito da 16 cifre [A-Z0-9]{16}]</t>
-  </si>
-  <si>
-    <t>[ERRORE-11| L'elemento ClinicalDocument/recordTarget/patientRole/addr DEVE riportare i sotto-elementi 'country', 'city' e 'streetAddressLine' ]</t>
-  </si>
-  <si>
-    <t>[ERRORE-14| L'elemento ClinicalDocument/recordTaget/patientRole/patient/name DEVE riportare gli elementi 'given' e 'family']</t>
-  </si>
-  <si>
-    <t>Almeno uno dei seguenti vocaboli non è censito: [CodeSystem: 2.16.840.1.113883.5.1 v2.1.0, Codes: VALORE_ERRATO]</t>
-  </si>
-  <si>
-    <t>ERROR: -1,-1 cvc-complex-type.2.4.a: Invalid content was found starting with element '{"urn:hl7-org:v3":priorityCode}'. One of '{"urn:hl7-org:v3":realmCode, "urn:hl7-org:v3":typeId, "urn:hl7-org:v3":templateId, "urn:hl7-org:v3":id}' is expected.</t>
-  </si>
-  <si>
-    <t>ERROR: -1,-1 cvc-complex-type.2.4.a: Invalid content was found starting with element '{"urn:hl7-org:v3":effectiveTime}'. One of '{"urn:hl7-org:v3":realmCode, "urn:hl7-org:v3":typeId, "urn:hl7-org:v3":templateId, "urn:hl7-org:v3":id, "urn:hl7-org:v3":code}' is expected.</t>
-  </si>
-  <si>
-    <t>[ERRORE-b4| Sezione Referto: la sezione DEVE essere presente],[ERRORE-b5| Sezione Referto: la sezione DEVE contenere un elemento 'text']</t>
-  </si>
-  <si>
-    <t>[ERRORE-b6| Sezione Quesito Diagnostico: la sezione DEVE contenere un elemento 'text']</t>
-  </si>
-  <si>
-    <t>ERROR: -1,-1 cvc-complex-type.2.4.b: The content of element 'entry' is not complete. One of '{"urn:hl7-org:v3":realmCode, "urn:hl7-org:v3":typeId, "urn:hl7-org:v3":templateId, "urn:hl7-org:v3":act, "urn:hl7-org:v3":encounter, "urn:hl7-org:v3":observation, "urn:hl7-org:v3":observationMedia, "urn:hl7-org:v3":organizer, "urn:hl7-org:v3":procedure, "urn:hl7-org:v3":regionOfInterest, "urn:hl7-org:v3":substanceAdministration, "urn:hl7-org:v3":supply}' is expected.</t>
-  </si>
-  <si>
-    <t>[ERRORE-b26| Sezione Storia Clinica: l'elemento entry/observation/effectiveTime deve essere presente e deve avere l'elemento 'low' valorizzato]</t>
-  </si>
-  <si>
-    <t>[ERRORE-b36| Sezione Storia Clinica: l'elemento entry/organizer/subject/relatedSubject deve avere l'attributo @classCode='PRS' e deve contenere l'elemento 'code']</t>
-  </si>
-  <si>
-    <t>[ERRORE-b53| Sotto-sezione Allergie: l'elemento entry/act/entryRelationship/observation/effectiveTime deve essere presente e deve avere l'elemento 'low' valorizzato ]</t>
-  </si>
-  <si>
-    <t>[ERRORE-b57| Sotto-sezione Allergie: entry/act/entryRelationship/observation deve contenere almeno un elemento 'participant']</t>
-  </si>
-  <si>
-    <t>[ERRORE-b22| Sezione Quesito Diagnostico: l'elemento entry/observation/value DEVE avere attributo @codeSystem valorizzato con l'OID del sistema di codifica ICD-9-CM ]</t>
-  </si>
-  <si>
-    <t>[ERRORE-30| L'elemento ClinicalDocument/legalAuthenticator/signatureCode deve essere valorizzato con il codice "S" ]</t>
-  </si>
-  <si>
-    <t>[ERRORE-b41| Sezione Storia Clinica: l'elemento entry/organizer/component/observation/value deve essere presente e valorizzato secondo il @codeSystem='2.16.840.1.113883.6.103' ]</t>
-  </si>
-  <si>
-    <t>ERROR: -1,-1 cvc-complex-type.2.4.a: Invalid content was found starting with element '{"urn:hl7-org:v3":languageCode}'. One of '{"urn:hl7-org:v3":confidentialityCode}' is expected.</t>
-  </si>
-  <si>
-    <t>Almeno uno dei seguenti vocaboli non è censito: [CodeSystem: 2.16.840.1.113883.5.7 v2.1.0, Codes: VALORE_ERRATO]</t>
-  </si>
-  <si>
-    <t>subject_application_id: Rehab-MS</t>
-  </si>
-  <si>
-    <t>subject_application_vendor: AISM</t>
-  </si>
-  <si>
-    <t>subject_application_version: 1.8</t>
+    <t>L'applicativo non gestisce le sezioni opzionali indicate nel test-case</t>
   </si>
 </sst>
 </file>
@@ -2816,7 +2822,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2980,9 +2986,6 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4466,7 +4469,9 @@
         <v>18</v>
       </c>
       <c r="B2" s="48"/>
-      <c r="C2" s="49"/>
+      <c r="C2" s="49" t="s">
+        <v>549</v>
+      </c>
       <c r="D2" s="48"/>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
@@ -4493,7 +4498,7 @@
       </c>
       <c r="B3" s="51"/>
       <c r="C3" s="56" t="s">
-        <v>630</v>
+        <v>546</v>
       </c>
       <c r="D3" s="48"/>
       <c r="F3" s="6"/>
@@ -4519,7 +4524,7 @@
       <c r="A4" s="52"/>
       <c r="B4" s="53"/>
       <c r="C4" s="56" t="s">
-        <v>631</v>
+        <v>547</v>
       </c>
       <c r="D4" s="48"/>
       <c r="E4" s="4"/>
@@ -4546,7 +4551,7 @@
       <c r="A5" s="54"/>
       <c r="B5" s="55"/>
       <c r="C5" s="56" t="s">
-        <v>632</v>
+        <v>548</v>
       </c>
       <c r="D5" s="48"/>
       <c r="F5" s="6"/>
@@ -4910,13 +4915,13 @@
         <v>46093</v>
       </c>
       <c r="G15" s="58" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="H15" s="59" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="I15" s="60" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="J15" s="36" t="s">
         <v>76</v>
@@ -4930,7 +4935,7 @@
         <v>76</v>
       </c>
       <c r="O15" s="36" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="P15" s="36" t="s">
         <v>76</v>
@@ -4942,7 +4947,7 @@
         <v>76</v>
       </c>
       <c r="S15" s="36" t="s">
-        <v>609</v>
+        <v>633</v>
       </c>
       <c r="T15" s="36"/>
       <c r="U15" s="36"/>
@@ -5230,13 +5235,13 @@
         <v>46093</v>
       </c>
       <c r="G23" s="58" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="H23" s="59" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="I23" s="60" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="J23" s="36" t="s">
         <v>76</v>
@@ -5250,7 +5255,7 @@
         <v>76</v>
       </c>
       <c r="O23" s="36" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="P23" s="36" t="s">
         <v>76</v>
@@ -5262,7 +5267,7 @@
         <v>76</v>
       </c>
       <c r="S23" s="36" t="s">
-        <v>609</v>
+        <v>633</v>
       </c>
       <c r="T23" s="36"/>
       <c r="U23" s="36"/>
@@ -5572,7 +5577,7 @@
         <v>76</v>
       </c>
       <c r="O31" s="36" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="P31" s="36" t="s">
         <v>76</v>
@@ -5584,7 +5589,7 @@
         <v>76</v>
       </c>
       <c r="S31" s="36" t="s">
-        <v>609</v>
+        <v>633</v>
       </c>
       <c r="T31" s="36"/>
       <c r="U31" s="36" t="s">
@@ -8729,13 +8734,13 @@
         <v>46093</v>
       </c>
       <c r="G116" s="58" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="H116" s="58" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="I116" s="58" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="J116" s="36" t="s">
         <v>76</v>
@@ -8749,7 +8754,7 @@
         <v>76</v>
       </c>
       <c r="O116" s="36" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="P116" s="36" t="s">
         <v>76</v>
@@ -8761,7 +8766,7 @@
         <v>76</v>
       </c>
       <c r="S116" s="36" t="s">
-        <v>609</v>
+        <v>633</v>
       </c>
       <c r="T116" s="36"/>
       <c r="U116" s="36"/>
@@ -8790,13 +8795,13 @@
         <v>46093</v>
       </c>
       <c r="G117" s="58" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="H117" s="58" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="I117" s="58" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="J117" s="36" t="s">
         <v>76</v>
@@ -8810,7 +8815,7 @@
         <v>76</v>
       </c>
       <c r="O117" s="36" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="P117" s="36" t="s">
         <v>76</v>
@@ -8822,7 +8827,7 @@
         <v>76</v>
       </c>
       <c r="S117" s="36" t="s">
-        <v>609</v>
+        <v>633</v>
       </c>
       <c r="T117" s="36"/>
       <c r="U117" s="36"/>
@@ -8851,13 +8856,13 @@
         <v>46093</v>
       </c>
       <c r="G118" s="58" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="H118" s="58" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="I118" s="58" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="J118" s="36" t="s">
         <v>76</v>
@@ -8871,7 +8876,7 @@
         <v>76</v>
       </c>
       <c r="O118" s="36" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="P118" s="36" t="s">
         <v>76</v>
@@ -8883,7 +8888,7 @@
         <v>76</v>
       </c>
       <c r="S118" s="36" t="s">
-        <v>609</v>
+        <v>633</v>
       </c>
       <c r="T118" s="36"/>
       <c r="U118" s="36"/>
@@ -8912,13 +8917,13 @@
         <v>46093</v>
       </c>
       <c r="G119" s="58" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="H119" s="58" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="I119" s="58" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="J119" s="36" t="s">
         <v>76</v>
@@ -8932,7 +8937,7 @@
         <v>76</v>
       </c>
       <c r="O119" s="36" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="P119" s="36" t="s">
         <v>76</v>
@@ -8944,7 +8949,7 @@
         <v>76</v>
       </c>
       <c r="S119" s="36" t="s">
-        <v>609</v>
+        <v>633</v>
       </c>
       <c r="T119" s="36"/>
       <c r="U119" s="36"/>
@@ -8973,13 +8978,13 @@
         <v>46093</v>
       </c>
       <c r="G120" s="58" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="H120" s="58" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="I120" s="58" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="J120" s="36" t="s">
         <v>76</v>
@@ -8993,7 +8998,7 @@
         <v>76</v>
       </c>
       <c r="O120" s="36" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="P120" s="36" t="s">
         <v>76</v>
@@ -9005,7 +9010,7 @@
         <v>76</v>
       </c>
       <c r="S120" s="36" t="s">
-        <v>609</v>
+        <v>633</v>
       </c>
       <c r="T120" s="36"/>
       <c r="U120" s="36"/>
@@ -9034,13 +9039,13 @@
         <v>46093</v>
       </c>
       <c r="G121" s="58" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="H121" s="58" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="I121" s="58" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="J121" s="36" t="s">
         <v>76</v>
@@ -9054,7 +9059,7 @@
         <v>76</v>
       </c>
       <c r="O121" s="36" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="P121" s="36" t="s">
         <v>76</v>
@@ -9066,7 +9071,7 @@
         <v>76</v>
       </c>
       <c r="S121" s="36" t="s">
-        <v>609</v>
+        <v>633</v>
       </c>
       <c r="T121" s="36"/>
       <c r="U121" s="36"/>
@@ -9095,13 +9100,13 @@
         <v>46093</v>
       </c>
       <c r="G122" s="58" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="H122" s="58" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="I122" s="58" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="J122" s="36" t="s">
         <v>76</v>
@@ -9115,7 +9120,7 @@
         <v>76</v>
       </c>
       <c r="O122" s="36" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="P122" s="36" t="s">
         <v>76</v>
@@ -9127,7 +9132,7 @@
         <v>76</v>
       </c>
       <c r="S122" s="36" t="s">
-        <v>609</v>
+        <v>633</v>
       </c>
       <c r="T122" s="36"/>
       <c r="U122" s="36"/>
@@ -9156,13 +9161,13 @@
         <v>46093</v>
       </c>
       <c r="G123" s="58" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="H123" s="58" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="I123" s="58" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="J123" s="36" t="s">
         <v>76</v>
@@ -9176,7 +9181,7 @@
         <v>76</v>
       </c>
       <c r="O123" s="36" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="P123" s="36" t="s">
         <v>76</v>
@@ -9188,7 +9193,7 @@
         <v>76</v>
       </c>
       <c r="S123" s="36" t="s">
-        <v>609</v>
+        <v>633</v>
       </c>
       <c r="T123" s="36"/>
       <c r="U123" s="36"/>
@@ -9217,13 +9222,13 @@
         <v>46093</v>
       </c>
       <c r="G124" s="58" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="H124" s="58" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="I124" s="58" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="J124" s="36" t="s">
         <v>76</v>
@@ -9237,7 +9242,7 @@
         <v>76</v>
       </c>
       <c r="O124" s="36" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="P124" s="36" t="s">
         <v>76</v>
@@ -9249,7 +9254,7 @@
         <v>76</v>
       </c>
       <c r="S124" s="36" t="s">
-        <v>609</v>
+        <v>633</v>
       </c>
       <c r="T124" s="36"/>
       <c r="U124" s="36"/>
@@ -9278,13 +9283,13 @@
         <v>46093</v>
       </c>
       <c r="G125" s="58" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="H125" s="58" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="I125" s="58" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="J125" s="36" t="s">
         <v>76</v>
@@ -9298,7 +9303,7 @@
         <v>76</v>
       </c>
       <c r="O125" s="36" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="P125" s="36" t="s">
         <v>76</v>
@@ -9310,7 +9315,7 @@
         <v>76</v>
       </c>
       <c r="S125" s="36" t="s">
-        <v>609</v>
+        <v>633</v>
       </c>
       <c r="T125" s="36"/>
       <c r="U125" s="36"/>
@@ -9339,13 +9344,13 @@
         <v>46093</v>
       </c>
       <c r="G126" s="58" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="H126" s="58" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="I126" s="58" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="J126" s="36" t="s">
         <v>76</v>
@@ -9359,7 +9364,7 @@
         <v>76</v>
       </c>
       <c r="O126" s="36" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="P126" s="36" t="s">
         <v>76</v>
@@ -9371,7 +9376,7 @@
         <v>76</v>
       </c>
       <c r="S126" s="36" t="s">
-        <v>609</v>
+        <v>633</v>
       </c>
       <c r="T126" s="36"/>
       <c r="U126" s="36"/>
@@ -9400,13 +9405,13 @@
         <v>46093</v>
       </c>
       <c r="G127" s="58" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="H127" s="58" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="I127" s="58" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="J127" s="36" t="s">
         <v>76</v>
@@ -9420,7 +9425,7 @@
         <v>76</v>
       </c>
       <c r="O127" s="36" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="P127" s="36" t="s">
         <v>76</v>
@@ -9432,7 +9437,7 @@
         <v>76</v>
       </c>
       <c r="S127" s="36" t="s">
-        <v>609</v>
+        <v>633</v>
       </c>
       <c r="T127" s="36"/>
       <c r="U127" s="36"/>
@@ -9461,13 +9466,13 @@
         <v>46093</v>
       </c>
       <c r="G128" s="58" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="H128" s="58" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="I128" s="58" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="J128" s="36" t="s">
         <v>76</v>
@@ -9481,7 +9486,7 @@
         <v>76</v>
       </c>
       <c r="O128" s="36" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="P128" s="36" t="s">
         <v>76</v>
@@ -9493,7 +9498,7 @@
         <v>76</v>
       </c>
       <c r="S128" s="36" t="s">
-        <v>609</v>
+        <v>633</v>
       </c>
       <c r="T128" s="36"/>
       <c r="U128" s="36"/>
@@ -9522,13 +9527,13 @@
         <v>46093</v>
       </c>
       <c r="G129" s="58" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="H129" s="58" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="I129" s="58" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="J129" s="36" t="s">
         <v>76</v>
@@ -9542,7 +9547,7 @@
         <v>76</v>
       </c>
       <c r="O129" s="36" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="P129" s="36" t="s">
         <v>76</v>
@@ -9554,7 +9559,7 @@
         <v>76</v>
       </c>
       <c r="S129" s="36" t="s">
-        <v>609</v>
+        <v>633</v>
       </c>
       <c r="T129" s="36"/>
       <c r="U129" s="36"/>
@@ -9583,13 +9588,13 @@
         <v>46093</v>
       </c>
       <c r="G130" s="58" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="H130" s="58" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="I130" s="58" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="J130" s="36" t="s">
         <v>76</v>
@@ -9603,7 +9608,7 @@
         <v>76</v>
       </c>
       <c r="O130" s="36" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="P130" s="36" t="s">
         <v>76</v>
@@ -9615,7 +9620,7 @@
         <v>76</v>
       </c>
       <c r="S130" s="36" t="s">
-        <v>609</v>
+        <v>633</v>
       </c>
       <c r="T130" s="36"/>
       <c r="U130" s="36"/>
@@ -10867,13 +10872,13 @@
         <v>46093</v>
       </c>
       <c r="G164" s="58" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="H164" s="58" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="I164" s="58" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="J164" s="36" t="s">
         <v>76</v>
@@ -10917,8 +10922,12 @@
       <c r="J165" s="36" t="s">
         <v>543</v>
       </c>
-      <c r="K165" s="36"/>
-      <c r="L165" s="36"/>
+      <c r="K165" s="36" t="s">
+        <v>506</v>
+      </c>
+      <c r="L165" s="36" t="s">
+        <v>634</v>
+      </c>
       <c r="M165" s="36"/>
       <c r="N165" s="36"/>
       <c r="O165" s="36"/>
@@ -11323,13 +11332,13 @@
         <v>46093</v>
       </c>
       <c r="G176" s="58" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="H176" s="58" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="I176" s="58" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="J176" s="36" t="s">
         <v>76</v>
@@ -11343,7 +11352,7 @@
         <v>76</v>
       </c>
       <c r="O176" s="36" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="P176" s="36" t="s">
         <v>76</v>
@@ -11355,7 +11364,7 @@
         <v>76</v>
       </c>
       <c r="S176" s="36" t="s">
-        <v>609</v>
+        <v>633</v>
       </c>
       <c r="T176" s="36"/>
       <c r="U176" s="33"/>
@@ -11606,13 +11615,13 @@
         <v>46093</v>
       </c>
       <c r="G183" s="58" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="H183" s="58" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="I183" s="58" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="J183" s="36" t="s">
         <v>76</v>
@@ -11626,7 +11635,7 @@
         <v>76</v>
       </c>
       <c r="O183" s="36" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="P183" s="36" t="s">
         <v>76</v>
@@ -11638,7 +11647,7 @@
         <v>76</v>
       </c>
       <c r="S183" s="36" t="s">
-        <v>609</v>
+        <v>633</v>
       </c>
       <c r="T183" s="36"/>
       <c r="U183" s="33"/>
@@ -11889,44 +11898,44 @@
         <v>46093</v>
       </c>
       <c r="G190" s="62" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="H190" s="62" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="I190" s="62" t="s">
-        <v>607</v>
-      </c>
-      <c r="J190" s="63" t="s">
+        <v>611</v>
+      </c>
+      <c r="J190" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="K190" s="63"/>
-      <c r="L190" s="63"/>
-      <c r="M190" s="63" t="s">
+      <c r="K190" s="36"/>
+      <c r="L190" s="36"/>
+      <c r="M190" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="N190" s="63" t="s">
+      <c r="N190" s="36" t="s">
         <v>76</v>
       </c>
       <c r="O190" s="63" t="s">
-        <v>629</v>
-      </c>
-      <c r="P190" s="63" t="s">
+        <v>632</v>
+      </c>
+      <c r="P190" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="Q190" s="63" t="s">
+      <c r="Q190" s="36" t="s">
         <v>543</v>
       </c>
-      <c r="R190" s="63" t="s">
+      <c r="R190" s="36" t="s">
         <v>76</v>
       </c>
       <c r="S190" s="63" t="s">
-        <v>609</v>
-      </c>
-      <c r="T190" s="63"/>
+        <v>633</v>
+      </c>
+      <c r="T190" s="36"/>
       <c r="U190" s="63"/>
-      <c r="V190" s="64"/>
-      <c r="W190" s="63" t="s">
+      <c r="V190" s="38"/>
+      <c r="W190" s="36" t="s">
         <v>50</v>
       </c>
     </row>
@@ -16977,19 +16986,19 @@
           <x14:formula1>
             <xm:f>Sheet1!$B$2:$B$3</xm:f>
           </x14:formula1>
-          <xm:sqref>M191:N245 P191:R245 M10:N14 J10:J14 P10:R14 P16:R22 M16:N22 J16:J22 J24:J30 P24:R30 M24:N30 M32:N115 J32:J115 P32:R115 M131:N163 J131:J163 P131:R163 J166:J175 P166:R175 M166:N175 M177:N182 J177:J182 P177:R182 P184:R189 M184:N189 J184:J189 J191:J245</xm:sqref>
+          <xm:sqref>M10:N245 J10:J245 P10:R245</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{70793024-27E9-4E6A-BACD-083AB683BC38}">
           <x14:formula1>
             <xm:f>Sheet1!$A$2:$A$3</xm:f>
           </x14:formula1>
-          <xm:sqref>T10:T14 T16:T22 T24:T30 T32:T115 T131:T163 T166:T175 T177:T182 T184:T189 T191:T245</xm:sqref>
+          <xm:sqref>T10:T245</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{3DE61C5E-9DA3-4CE3-A1FF-8FBE651EA6B5}">
           <x14:formula1>
             <xm:f>'LISTA VALORI'!$A$2:$A$8</xm:f>
           </x14:formula1>
-          <xm:sqref>K10:K14 K16:K22 K24:K30 K32:K115 K131:K163 K166:K175 K177:K182 K184:K189 K191:K245</xm:sqref>
+          <xm:sqref>K10:K245</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/GATEWAY/A1#111#AISMXX/AISM/Rehab-MS/1.8/accreditamento-checklist_V8.3.0.xlsx
+++ b/GATEWAY/A1#111#AISMXX/AISM/Rehab-MS/1.8/accreditamento-checklist_V8.3.0.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gaetano.paterno\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://relatech-my.sharepoint.com/personal/gaetano_paterno_relatech_com/Documents/Documenti/AISM/Accreditamento - t4 - 24-03-2026/A1#111#AISMXXAISMRehab-MS1.8/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14C1AD8A-E3BE-4F27-A94B-B21A7F4EA211}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="91" documentId="13_ncr:1_{14C1AD8A-E3BE-4F27-A94B-B21A7F4EA211}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B02F2BCB-1F75-444F-95AD-78C48586C9B6}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="1620" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2098,192 +2098,9 @@
     <t>AISM</t>
   </si>
   <si>
-    <t>2026-03-12T16:02:00Z</t>
-  </si>
-  <si>
-    <t>a562280c170e8f7bcb9ae0620514d345</t>
-  </si>
-  <si>
     <t>UNKNOWN_WORKFLOW_ID</t>
   </si>
   <si>
-    <t>2026-03-12T16:21:00Z</t>
-  </si>
-  <si>
-    <t>3d9719cc9d371becd1a98db86999c191</t>
-  </si>
-  <si>
-    <t>2026-03-12T12:11:00Z</t>
-  </si>
-  <si>
-    <t>5cb2365d52b4faf5e5c3d2d765b3b373</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.4.1.5.4ec2294d7090fdb09a5f15a8f56851e79825ade06c3904a83ae3c305386184f9.15ce590e4a^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2026-03-12T11:46:34Z</t>
-  </si>
-  <si>
-    <t>feb68301551288a8af297401a92058f0</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.4.1.5.4ec2294d7090fdb09a5f15a8f56851e79825ade06c3904a83ae3c305386184f9.c4b7364030^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2026-03-12T11:49:10Z</t>
-  </si>
-  <si>
-    <t>8a649703df5ce5458e8ee3c8abbb8b31</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.4.1.5.4ec2294d7090fdb09a5f15a8f56851e79825ade06c3904a83ae3c305386184f9.60b1f9b424^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2026-03-12T11:51:25Z</t>
-  </si>
-  <si>
-    <t>90915c07eb87083e89b59397fe55d7b1</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.4.1.5.4ec2294d7090fdb09a5f15a8f56851e79825ade06c3904a83ae3c305386184f9.5ea86cd414^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2026-03-12T12:05:17Z</t>
-  </si>
-  <si>
-    <t>42896180da70719226a6e1fa71f636f5</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.4.1.5.4ec2294d7090fdb09a5f15a8f56851e79825ade06c3904a83ae3c305386184f9.dd90425c63^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2026-03-12T12:22:13Z</t>
-  </si>
-  <si>
-    <t>912a4ee0fa40a523ea6248bb735e005d</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.4.1.5.4ec2294d7090fdb09a5f15a8f56851e79825ade06c3904a83ae3c305386184f9.091236b459^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2026-03-12T12:23:32Z</t>
-  </si>
-  <si>
-    <t>0efcd8ae4be8fa99586a443590ac770b</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.4.1.5.4ec2294d7090fdb09a5f15a8f56851e79825ade06c3904a83ae3c305386184f9.698cb15a86^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2026-03-12T12:25:13Z</t>
-  </si>
-  <si>
-    <t>ca2ec3f58775dabb9ff4200323d84d30</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.4.1.5.4ec2294d7090fdb09a5f15a8f56851e79825ade06c3904a83ae3c305386184f9.8e0b123248^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2026-03-12T12:27:55Z</t>
-  </si>
-  <si>
-    <t>4bfc6e7841d888c92e9f6fb21a0bf771</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.4.1.5.4ec2294d7090fdb09a5f15a8f56851e79825ade06c3904a83ae3c305386184f9.fb0b77daa2^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2026-03-12T12:32:51Z</t>
-  </si>
-  <si>
-    <t>2c22f3d1a6c7b4042c6a237d0038ead8</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.4.1.5.4ec2294d7090fdb09a5f15a8f56851e79825ade06c3904a83ae3c305386184f9.ef91924fe8^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2026-03-12T12:34:59Z</t>
-  </si>
-  <si>
-    <t>521c5c6333cd08aa8e746723b81b3e92</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.4.1.5.4ec2294d7090fdb09a5f15a8f56851e79825ade06c3904a83ae3c305386184f9.c981c652ce^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2026-03-12T12:34:39Z</t>
-  </si>
-  <si>
-    <t>105e6cfa96e009d9c0f56cee918d2a82</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.4.1.5.4ec2294d7090fdb09a5f15a8f56851e79825ade06c3904a83ae3c305386184f9.f4ab2957d1^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2026-03-12T12:36:32Z</t>
-  </si>
-  <si>
-    <t>238ed68f4ddf530a7771bff2f6ef0130</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.4.1.5.4ec2294d7090fdb09a5f15a8f56851e79825ade06c3904a83ae3c305386184f9.c8d04334ef^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2026-03-12T12:38:39Z</t>
-  </si>
-  <si>
-    <t>94fd185e81f15cd45a62eeefcbb96fe8</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.4.1.5.4ec2294d7090fdb09a5f15a8f56851e79825ade06c3904a83ae3c305386184f9.c08e38318f^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2026-03-12T12:42:57Z</t>
-  </si>
-  <si>
-    <t>a9de2005f76eee2f7351ac8bc97ad2cc</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.4.1.5.4ec2294d7090fdb09a5f15a8f56851e79825ade06c3904a83ae3c305386184f9.d19c199773^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2026-03-12T12:43:30Z</t>
-  </si>
-  <si>
-    <t>53b9fa6a79a2300d130cb119ab82a6f6</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.4.1.5.4ec2294d7090fdb09a5f15a8f56851e79825ade06c3904a83ae3c305386184f9.74bfdab708^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2026-03-12T12:45:31Z</t>
-  </si>
-  <si>
-    <t>1ed76fa05d13f747cc6687de0592ba4c</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.4.1.5.4ec2294d7090fdb09a5f15a8f56851e79825ade06c3904a83ae3c305386184f9.57fcd01901^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2026-03-12T12:48:33Z</t>
-  </si>
-  <si>
-    <t>35b8bd7bfb098dcfc621e9de8ef41e19</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.4.1.5.4ec2294d7090fdb09a5f15a8f56851e79825ade06c3904a83ae3c305386184f9.fa73ff2bfd^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2026-03-12T12:51:21Z</t>
-  </si>
-  <si>
-    <t>836de80b27fad9d7d698f74be4bbc4e0</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.4.1.5.4ec2294d7090fdb09a5f15a8f56851e79825ade06c3904a83ae3c305386184f9.b1181008a7^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
     <t>title:"Campo token JWT non valido.","detail":"Il campo purpose_of_use non è valorizzato","status":403</t>
   </si>
   <si>
@@ -2293,9 +2110,6 @@
     <t>TIMEOUT</t>
   </si>
   <si>
-    <t>[ERRORE-44| Il codice fiscale 'pznttf80a50d548v' cittadino ed operatore deve essere costituito da 16 cifre [A-Z0-9]{16}],[ERRORE-44| Il codice fiscale 'mrrssi87d52s969a' cittadino ed operatore deve essere costituito da 16 cifre [A-Z0-9]{16}],[ERRORE-44| Il codice fiscale 'mrrssi87d52s969a' cittadino ed operatore deve essere costituito da 16 cifre [A-Z0-9]{16}]</t>
-  </si>
-  <si>
     <t>[ERRORE-11| L'elemento ClinicalDocument/recordTarget/patientRole/addr DEVE riportare i sotto-elementi 'country', 'city' e 'streetAddressLine' ]</t>
   </si>
   <si>
@@ -2351,6 +2165,192 @@
   </si>
   <si>
     <t>L'applicativo non gestisce le sezioni opzionali indicate nel test-case</t>
+  </si>
+  <si>
+    <t>2026-03-24T15:23:31Z</t>
+  </si>
+  <si>
+    <t>2026-03-24T15:22:25Z</t>
+  </si>
+  <si>
+    <t>2026-03-24T15:18:49Z</t>
+  </si>
+  <si>
+    <t>2026-03-24T15:20:06Z</t>
+  </si>
+  <si>
+    <t>2026-03-24T15:21:10Z</t>
+  </si>
+  <si>
+    <t>2026-03-24T14:40:15Z</t>
+  </si>
+  <si>
+    <t>2026-03-24T14:53:57Z</t>
+  </si>
+  <si>
+    <t>2026-03-24T14:55:46Z</t>
+  </si>
+  <si>
+    <t>2026-03-24T14:56:49Z</t>
+  </si>
+  <si>
+    <t>2026-03-24T14:57:56Z</t>
+  </si>
+  <si>
+    <t>2026-03-24T15:03:04Z</t>
+  </si>
+  <si>
+    <t>2026-03-24T15:04:01Z</t>
+  </si>
+  <si>
+    <t>2026-03-24T15:05:03Z</t>
+  </si>
+  <si>
+    <t>2026-03-24T15:06:04Z</t>
+  </si>
+  <si>
+    <t>2026-03-24T15:07:07Z</t>
+  </si>
+  <si>
+    <t>2026-03-24T15:08:02Z</t>
+  </si>
+  <si>
+    <t>2026-03-24T15:09:16Z</t>
+  </si>
+  <si>
+    <t>2026-03-24T15:10:09Z</t>
+  </si>
+  <si>
+    <t>2026-03-24T15:11:14Z</t>
+  </si>
+  <si>
+    <t>2026-03-24T15:12:38Z</t>
+  </si>
+  <si>
+    <t>2026-03-24T15:13:54Z</t>
+  </si>
+  <si>
+    <t>13c2a3b526c6e11d945007ad3d68ac3e</t>
+  </si>
+  <si>
+    <t>e29884fabbedc2e8a7e0dc18ae668920</t>
+  </si>
+  <si>
+    <t>67a3029fa9d3270bb8bcbf98a7bef3de</t>
+  </si>
+  <si>
+    <t>fe8ce38086901e41caeb0ee755a10502</t>
+  </si>
+  <si>
+    <t>9ac987880d3813ff0cd84ec2e8fb54ed</t>
+  </si>
+  <si>
+    <t>e2f3e2b36b017e1186614b5d075b7d6d</t>
+  </si>
+  <si>
+    <t>f8c943813e6e9d4c644e23e60a6dfd7d</t>
+  </si>
+  <si>
+    <t>01f7b5f5891be3ea068727705968bde5</t>
+  </si>
+  <si>
+    <t>3ac0afff178fd5f06fc7fd00826617b5</t>
+  </si>
+  <si>
+    <t>faab16fb1366354acf1a7182cdb826a2</t>
+  </si>
+  <si>
+    <t>28c50eeffd75d0d58eff52cd98e59a1d</t>
+  </si>
+  <si>
+    <t>d327c4c4db2305c7cf96932b388acd8e</t>
+  </si>
+  <si>
+    <t>0ff0a40365cd78f1351117ec8b428af0</t>
+  </si>
+  <si>
+    <t>f578315ac14f96207856b09cb10e1703</t>
+  </si>
+  <si>
+    <t>81bab8e866598d108c3b1687e22a7e16</t>
+  </si>
+  <si>
+    <t>46f4f6c75cca2982b7f629003bfaaf26</t>
+  </si>
+  <si>
+    <t>8fb59ccafae8eff45f357d47410e8532</t>
+  </si>
+  <si>
+    <t>0eaeece6c59c6c0b13fb2f3eb2745973</t>
+  </si>
+  <si>
+    <t>2dc1ea91443452878e11bdc47ab2f565</t>
+  </si>
+  <si>
+    <t>fe32e28c736e259319d3935b56e2eaa7</t>
+  </si>
+  <si>
+    <t>5a7dfc18e62a8aa4d68af6f071e1c08a</t>
+  </si>
+  <si>
+    <t>[ERRORE-44| Il codice fiscale 'pznttf80a50d548v' cittadino ed operatore deve essere costituito da 16 cifre [A-Z0-9]{16}],[ERRORE-44| Il codice fiscale 'dmndnd84l28a326h' cittadino ed operatore deve essere costituito da 16 cifre [A-Z0-9]{16}],[ERRORE-44| Il codice fiscale 'dmndnd84l28a326h' cittadino ed operatore deve essere costituito da 16 cifre [A-Z0-9]{16}]</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.4.1.5.4ec2294d7090fdb09a5f15a8f56851e79825ade06c3904a83ae3c305386184f9.1c7461f098^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.4.1.5.4ec2294d7090fdb09a5f15a8f56851e79825ade06c3904a83ae3c305386184f9.422cf1a7ae^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.4.1.5.4ec2294d7090fdb09a5f15a8f56851e79825ade06c3904a83ae3c305386184f9.7feadf6303^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.4.1.5.4ec2294d7090fdb09a5f15a8f56851e79825ade06c3904a83ae3c305386184f9.380a230847^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.4.1.5.4ec2294d7090fdb09a5f15a8f56851e79825ade06c3904a83ae3c305386184f9.aa5a1d3ab7^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.4.1.5.4ec2294d7090fdb09a5f15a8f56851e79825ade06c3904a83ae3c305386184f9.2b5f9cb0f7^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.4.1.5.4ec2294d7090fdb09a5f15a8f56851e79825ade06c3904a83ae3c305386184f9.4c64ce6798^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.4.1.5.4ec2294d7090fdb09a5f15a8f56851e79825ade06c3904a83ae3c305386184f9.24fccc0770^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.4.1.5.4ec2294d7090fdb09a5f15a8f56851e79825ade06c3904a83ae3c305386184f9.52960582f8^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.4.1.5.4ec2294d7090fdb09a5f15a8f56851e79825ade06c3904a83ae3c305386184f9.021db326dd^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.4.1.5.4ec2294d7090fdb09a5f15a8f56851e79825ade06c3904a83ae3c305386184f9.816e154784^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.4.1.5.4ec2294d7090fdb09a5f15a8f56851e79825ade06c3904a83ae3c305386184f9.9f60c4cdbb^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.4.1.5.4ec2294d7090fdb09a5f15a8f56851e79825ade06c3904a83ae3c305386184f9.a52238ff93^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.4.1.5.4ec2294d7090fdb09a5f15a8f56851e79825ade06c3904a83ae3c305386184f9.836e1d0f95^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.4.1.5.4ec2294d7090fdb09a5f15a8f56851e79825ade06c3904a83ae3c305386184f9.3bd4f7a3ac^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.4.1.5.4ec2294d7090fdb09a5f15a8f56851e79825ade06c3904a83ae3c305386184f9.8c964dcbd9^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.4.1.5.4ec2294d7090fdb09a5f15a8f56851e79825ade06c3904a83ae3c305386184f9.d784acc49f^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.4.1.5.4ec2294d7090fdb09a5f15a8f56851e79825ade06c3904a83ae3c305386184f9.c3dbfa66a0^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.4.1.5.4ec2294d7090fdb09a5f15a8f56851e79825ade06c3904a83ae3c305386184f9.84f83b87a9^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
 </sst>
 </file>
@@ -2822,7 +2822,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2944,6 +2944,21 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2965,27 +2980,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="16" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4465,14 +4459,14 @@
       <c r="W1" s="9"/>
     </row>
     <row r="2" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="47" t="s">
+      <c r="A2" s="52" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="48"/>
-      <c r="C2" s="49" t="s">
+      <c r="B2" s="53"/>
+      <c r="C2" s="54" t="s">
         <v>549</v>
       </c>
-      <c r="D2" s="48"/>
+      <c r="D2" s="53"/>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
       <c r="H2" s="6"/>
@@ -4493,14 +4487,14 @@
       <c r="W2" s="9"/>
     </row>
     <row r="3" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="50" t="s">
+      <c r="A3" s="55" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="51"/>
-      <c r="C3" s="56" t="s">
+      <c r="B3" s="56"/>
+      <c r="C3" s="61" t="s">
         <v>546</v>
       </c>
-      <c r="D3" s="48"/>
+      <c r="D3" s="53"/>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
       <c r="H3" s="6"/>
@@ -4521,12 +4515,12 @@
       <c r="W3" s="9"/>
     </row>
     <row r="4" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="52"/>
-      <c r="B4" s="53"/>
-      <c r="C4" s="56" t="s">
+      <c r="A4" s="57"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="61" t="s">
         <v>547</v>
       </c>
-      <c r="D4" s="48"/>
+      <c r="D4" s="53"/>
       <c r="E4" s="4"/>
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
@@ -4548,12 +4542,12 @@
       <c r="W4" s="9"/>
     </row>
     <row r="5" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="54"/>
-      <c r="B5" s="55"/>
-      <c r="C5" s="56" t="s">
+      <c r="A5" s="59"/>
+      <c r="B5" s="60"/>
+      <c r="C5" s="61" t="s">
         <v>548</v>
       </c>
-      <c r="D5" s="48"/>
+      <c r="D5" s="53"/>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
@@ -4574,8 +4568,8 @@
       <c r="W5" s="9"/>
     </row>
     <row r="6" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="45"/>
-      <c r="B6" s="46"/>
+      <c r="A6" s="50"/>
+      <c r="B6" s="51"/>
       <c r="C6" s="10"/>
       <c r="F6" s="6"/>
       <c r="G6" s="6"/>
@@ -4911,17 +4905,17 @@
       <c r="E15" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="F15" s="57">
-        <v>46093</v>
-      </c>
-      <c r="G15" s="58" t="s">
+      <c r="F15" s="45">
+        <v>46105</v>
+      </c>
+      <c r="G15" s="46" t="s">
+        <v>573</v>
+      </c>
+      <c r="H15" s="47" t="s">
+        <v>594</v>
+      </c>
+      <c r="I15" s="48" t="s">
         <v>550</v>
-      </c>
-      <c r="H15" s="59" t="s">
-        <v>551</v>
-      </c>
-      <c r="I15" s="60" t="s">
-        <v>552</v>
       </c>
       <c r="J15" s="36" t="s">
         <v>76</v>
@@ -4935,7 +4929,7 @@
         <v>76</v>
       </c>
       <c r="O15" s="36" t="s">
-        <v>612</v>
+        <v>551</v>
       </c>
       <c r="P15" s="36" t="s">
         <v>76</v>
@@ -4947,7 +4941,7 @@
         <v>76</v>
       </c>
       <c r="S15" s="36" t="s">
-        <v>633</v>
+        <v>571</v>
       </c>
       <c r="T15" s="36"/>
       <c r="U15" s="36"/>
@@ -5231,17 +5225,17 @@
       <c r="E23" s="41" t="s">
         <v>66</v>
       </c>
-      <c r="F23" s="57">
-        <v>46093</v>
-      </c>
-      <c r="G23" s="58" t="s">
-        <v>553</v>
-      </c>
-      <c r="H23" s="59" t="s">
-        <v>554</v>
-      </c>
-      <c r="I23" s="60" t="s">
-        <v>552</v>
+      <c r="F23" s="45">
+        <v>46105</v>
+      </c>
+      <c r="G23" s="46" t="s">
+        <v>574</v>
+      </c>
+      <c r="H23" s="47" t="s">
+        <v>595</v>
+      </c>
+      <c r="I23" s="48" t="s">
+        <v>550</v>
       </c>
       <c r="J23" s="36" t="s">
         <v>76</v>
@@ -5255,7 +5249,7 @@
         <v>76</v>
       </c>
       <c r="O23" s="36" t="s">
-        <v>613</v>
+        <v>552</v>
       </c>
       <c r="P23" s="36" t="s">
         <v>76</v>
@@ -5267,7 +5261,7 @@
         <v>76</v>
       </c>
       <c r="S23" s="36" t="s">
-        <v>633</v>
+        <v>571</v>
       </c>
       <c r="T23" s="36"/>
       <c r="U23" s="36"/>
@@ -5559,12 +5553,12 @@
       <c r="E31" s="41" t="s">
         <v>75</v>
       </c>
-      <c r="F31" s="57">
-        <v>46093</v>
-      </c>
-      <c r="G31" s="59"/>
-      <c r="H31" s="59"/>
-      <c r="I31" s="60"/>
+      <c r="F31" s="45">
+        <v>46105</v>
+      </c>
+      <c r="G31" s="47"/>
+      <c r="H31" s="47"/>
+      <c r="I31" s="48"/>
       <c r="J31" s="36" t="s">
         <v>76</v>
       </c>
@@ -5577,7 +5571,7 @@
         <v>76</v>
       </c>
       <c r="O31" s="36" t="s">
-        <v>614</v>
+        <v>553</v>
       </c>
       <c r="P31" s="36" t="s">
         <v>76</v>
@@ -5589,7 +5583,7 @@
         <v>76</v>
       </c>
       <c r="S31" s="36" t="s">
-        <v>633</v>
+        <v>571</v>
       </c>
       <c r="T31" s="36"/>
       <c r="U31" s="36" t="s">
@@ -8730,17 +8724,17 @@
       <c r="E116" s="41" t="s">
         <v>247</v>
       </c>
-      <c r="F116" s="57">
-        <v>46093</v>
-      </c>
-      <c r="G116" s="58" t="s">
-        <v>555</v>
-      </c>
-      <c r="H116" s="58" t="s">
-        <v>556</v>
-      </c>
-      <c r="I116" s="58" t="s">
-        <v>557</v>
+      <c r="F116" s="45">
+        <v>46105</v>
+      </c>
+      <c r="G116" s="46" t="s">
+        <v>575</v>
+      </c>
+      <c r="H116" s="46" t="s">
+        <v>596</v>
+      </c>
+      <c r="I116" s="46" t="s">
+        <v>616</v>
       </c>
       <c r="J116" s="36" t="s">
         <v>76</v>
@@ -8766,7 +8760,7 @@
         <v>76</v>
       </c>
       <c r="S116" s="36" t="s">
-        <v>633</v>
+        <v>571</v>
       </c>
       <c r="T116" s="36"/>
       <c r="U116" s="36"/>
@@ -8791,17 +8785,17 @@
       <c r="E117" s="41" t="s">
         <v>249</v>
       </c>
-      <c r="F117" s="57">
-        <v>46093</v>
-      </c>
-      <c r="G117" s="58" t="s">
-        <v>558</v>
-      </c>
-      <c r="H117" s="58" t="s">
-        <v>559</v>
-      </c>
-      <c r="I117" s="58" t="s">
-        <v>560</v>
+      <c r="F117" s="45">
+        <v>46105</v>
+      </c>
+      <c r="G117" s="46" t="s">
+        <v>576</v>
+      </c>
+      <c r="H117" s="46" t="s">
+        <v>597</v>
+      </c>
+      <c r="I117" s="46" t="s">
+        <v>617</v>
       </c>
       <c r="J117" s="36" t="s">
         <v>76</v>
@@ -8815,7 +8809,7 @@
         <v>76</v>
       </c>
       <c r="O117" s="36" t="s">
-        <v>616</v>
+        <v>554</v>
       </c>
       <c r="P117" s="36" t="s">
         <v>76</v>
@@ -8827,7 +8821,7 @@
         <v>76</v>
       </c>
       <c r="S117" s="36" t="s">
-        <v>633</v>
+        <v>571</v>
       </c>
       <c r="T117" s="36"/>
       <c r="U117" s="36"/>
@@ -8852,17 +8846,17 @@
       <c r="E118" s="41" t="s">
         <v>251</v>
       </c>
-      <c r="F118" s="57">
-        <v>46093</v>
-      </c>
-      <c r="G118" s="58" t="s">
-        <v>561</v>
-      </c>
-      <c r="H118" s="58" t="s">
-        <v>562</v>
-      </c>
-      <c r="I118" s="58" t="s">
-        <v>563</v>
+      <c r="F118" s="45">
+        <v>46105</v>
+      </c>
+      <c r="G118" s="46" t="s">
+        <v>577</v>
+      </c>
+      <c r="H118" s="46" t="s">
+        <v>598</v>
+      </c>
+      <c r="I118" s="46" t="s">
+        <v>618</v>
       </c>
       <c r="J118" s="36" t="s">
         <v>76</v>
@@ -8876,7 +8870,7 @@
         <v>76</v>
       </c>
       <c r="O118" s="36" t="s">
-        <v>617</v>
+        <v>555</v>
       </c>
       <c r="P118" s="36" t="s">
         <v>76</v>
@@ -8888,7 +8882,7 @@
         <v>76</v>
       </c>
       <c r="S118" s="36" t="s">
-        <v>633</v>
+        <v>571</v>
       </c>
       <c r="T118" s="36"/>
       <c r="U118" s="36"/>
@@ -8913,17 +8907,17 @@
       <c r="E119" s="41" t="s">
         <v>253</v>
       </c>
-      <c r="F119" s="57">
-        <v>46093</v>
-      </c>
-      <c r="G119" s="58" t="s">
-        <v>564</v>
-      </c>
-      <c r="H119" s="58" t="s">
-        <v>565</v>
-      </c>
-      <c r="I119" s="58" t="s">
-        <v>566</v>
+      <c r="F119" s="45">
+        <v>46105</v>
+      </c>
+      <c r="G119" s="46" t="s">
+        <v>578</v>
+      </c>
+      <c r="H119" s="46" t="s">
+        <v>599</v>
+      </c>
+      <c r="I119" s="46" t="s">
+        <v>619</v>
       </c>
       <c r="J119" s="36" t="s">
         <v>76</v>
@@ -8937,7 +8931,7 @@
         <v>76</v>
       </c>
       <c r="O119" s="36" t="s">
-        <v>618</v>
+        <v>556</v>
       </c>
       <c r="P119" s="36" t="s">
         <v>76</v>
@@ -8949,7 +8943,7 @@
         <v>76</v>
       </c>
       <c r="S119" s="36" t="s">
-        <v>633</v>
+        <v>571</v>
       </c>
       <c r="T119" s="36"/>
       <c r="U119" s="36"/>
@@ -8974,17 +8968,17 @@
       <c r="E120" s="41" t="s">
         <v>255</v>
       </c>
-      <c r="F120" s="57">
-        <v>46093</v>
-      </c>
-      <c r="G120" s="58" t="s">
-        <v>567</v>
-      </c>
-      <c r="H120" s="58" t="s">
-        <v>568</v>
-      </c>
-      <c r="I120" s="58" t="s">
-        <v>569</v>
+      <c r="F120" s="45">
+        <v>46105</v>
+      </c>
+      <c r="G120" s="46" t="s">
+        <v>579</v>
+      </c>
+      <c r="H120" s="46" t="s">
+        <v>600</v>
+      </c>
+      <c r="I120" s="46" t="s">
+        <v>620</v>
       </c>
       <c r="J120" s="36" t="s">
         <v>76</v>
@@ -8998,7 +8992,7 @@
         <v>76</v>
       </c>
       <c r="O120" s="36" t="s">
-        <v>619</v>
+        <v>557</v>
       </c>
       <c r="P120" s="36" t="s">
         <v>76</v>
@@ -9010,7 +9004,7 @@
         <v>76</v>
       </c>
       <c r="S120" s="36" t="s">
-        <v>633</v>
+        <v>571</v>
       </c>
       <c r="T120" s="36"/>
       <c r="U120" s="36"/>
@@ -9035,17 +9029,17 @@
       <c r="E121" s="41" t="s">
         <v>257</v>
       </c>
-      <c r="F121" s="57">
-        <v>46093</v>
-      </c>
-      <c r="G121" s="58" t="s">
-        <v>570</v>
-      </c>
-      <c r="H121" s="58" t="s">
-        <v>571</v>
-      </c>
-      <c r="I121" s="58" t="s">
-        <v>572</v>
+      <c r="F121" s="45">
+        <v>46105</v>
+      </c>
+      <c r="G121" s="46" t="s">
+        <v>580</v>
+      </c>
+      <c r="H121" s="46" t="s">
+        <v>601</v>
+      </c>
+      <c r="I121" s="46" t="s">
+        <v>621</v>
       </c>
       <c r="J121" s="36" t="s">
         <v>76</v>
@@ -9059,7 +9053,7 @@
         <v>76</v>
       </c>
       <c r="O121" s="36" t="s">
-        <v>620</v>
+        <v>558</v>
       </c>
       <c r="P121" s="36" t="s">
         <v>76</v>
@@ -9071,7 +9065,7 @@
         <v>76</v>
       </c>
       <c r="S121" s="36" t="s">
-        <v>633</v>
+        <v>571</v>
       </c>
       <c r="T121" s="36"/>
       <c r="U121" s="36"/>
@@ -9096,17 +9090,17 @@
       <c r="E122" s="41" t="s">
         <v>259</v>
       </c>
-      <c r="F122" s="57">
-        <v>46093</v>
-      </c>
-      <c r="G122" s="58" t="s">
-        <v>573</v>
-      </c>
-      <c r="H122" s="58" t="s">
-        <v>574</v>
-      </c>
-      <c r="I122" s="58" t="s">
-        <v>575</v>
+      <c r="F122" s="45">
+        <v>46105</v>
+      </c>
+      <c r="G122" s="46" t="s">
+        <v>581</v>
+      </c>
+      <c r="H122" s="46" t="s">
+        <v>602</v>
+      </c>
+      <c r="I122" s="46" t="s">
+        <v>622</v>
       </c>
       <c r="J122" s="36" t="s">
         <v>76</v>
@@ -9120,7 +9114,7 @@
         <v>76</v>
       </c>
       <c r="O122" s="36" t="s">
-        <v>621</v>
+        <v>559</v>
       </c>
       <c r="P122" s="36" t="s">
         <v>76</v>
@@ -9132,7 +9126,7 @@
         <v>76</v>
       </c>
       <c r="S122" s="36" t="s">
-        <v>633</v>
+        <v>571</v>
       </c>
       <c r="T122" s="36"/>
       <c r="U122" s="36"/>
@@ -9157,17 +9151,17 @@
       <c r="E123" s="41" t="s">
         <v>261</v>
       </c>
-      <c r="F123" s="57">
-        <v>46093</v>
-      </c>
-      <c r="G123" s="58" t="s">
-        <v>576</v>
-      </c>
-      <c r="H123" s="58" t="s">
-        <v>577</v>
-      </c>
-      <c r="I123" s="58" t="s">
-        <v>578</v>
+      <c r="F123" s="45">
+        <v>46105</v>
+      </c>
+      <c r="G123" s="46" t="s">
+        <v>582</v>
+      </c>
+      <c r="H123" s="46" t="s">
+        <v>603</v>
+      </c>
+      <c r="I123" s="46" t="s">
+        <v>623</v>
       </c>
       <c r="J123" s="36" t="s">
         <v>76</v>
@@ -9181,7 +9175,7 @@
         <v>76</v>
       </c>
       <c r="O123" s="36" t="s">
-        <v>622</v>
+        <v>560</v>
       </c>
       <c r="P123" s="36" t="s">
         <v>76</v>
@@ -9193,7 +9187,7 @@
         <v>76</v>
       </c>
       <c r="S123" s="36" t="s">
-        <v>633</v>
+        <v>571</v>
       </c>
       <c r="T123" s="36"/>
       <c r="U123" s="36"/>
@@ -9218,17 +9212,17 @@
       <c r="E124" s="41" t="s">
         <v>263</v>
       </c>
-      <c r="F124" s="57">
-        <v>46093</v>
-      </c>
-      <c r="G124" s="58" t="s">
-        <v>579</v>
-      </c>
-      <c r="H124" s="58" t="s">
-        <v>580</v>
-      </c>
-      <c r="I124" s="58" t="s">
-        <v>581</v>
+      <c r="F124" s="45">
+        <v>46105</v>
+      </c>
+      <c r="G124" s="46" t="s">
+        <v>583</v>
+      </c>
+      <c r="H124" s="46" t="s">
+        <v>604</v>
+      </c>
+      <c r="I124" s="46" t="s">
+        <v>624</v>
       </c>
       <c r="J124" s="36" t="s">
         <v>76</v>
@@ -9242,7 +9236,7 @@
         <v>76</v>
       </c>
       <c r="O124" s="36" t="s">
-        <v>623</v>
+        <v>561</v>
       </c>
       <c r="P124" s="36" t="s">
         <v>76</v>
@@ -9254,7 +9248,7 @@
         <v>76</v>
       </c>
       <c r="S124" s="36" t="s">
-        <v>633</v>
+        <v>571</v>
       </c>
       <c r="T124" s="36"/>
       <c r="U124" s="36"/>
@@ -9279,17 +9273,17 @@
       <c r="E125" s="41" t="s">
         <v>265</v>
       </c>
-      <c r="F125" s="57">
-        <v>46093</v>
-      </c>
-      <c r="G125" s="58" t="s">
-        <v>582</v>
-      </c>
-      <c r="H125" s="58" t="s">
-        <v>583</v>
-      </c>
-      <c r="I125" s="58" t="s">
+      <c r="F125" s="45">
+        <v>46105</v>
+      </c>
+      <c r="G125" s="46" t="s">
         <v>584</v>
+      </c>
+      <c r="H125" s="46" t="s">
+        <v>605</v>
+      </c>
+      <c r="I125" s="46" t="s">
+        <v>625</v>
       </c>
       <c r="J125" s="36" t="s">
         <v>76</v>
@@ -9303,7 +9297,7 @@
         <v>76</v>
       </c>
       <c r="O125" s="36" t="s">
-        <v>624</v>
+        <v>562</v>
       </c>
       <c r="P125" s="36" t="s">
         <v>76</v>
@@ -9315,7 +9309,7 @@
         <v>76</v>
       </c>
       <c r="S125" s="36" t="s">
-        <v>633</v>
+        <v>571</v>
       </c>
       <c r="T125" s="36"/>
       <c r="U125" s="36"/>
@@ -9340,17 +9334,17 @@
       <c r="E126" s="41" t="s">
         <v>267</v>
       </c>
-      <c r="F126" s="57">
-        <v>46093</v>
-      </c>
-      <c r="G126" s="58" t="s">
+      <c r="F126" s="45">
+        <v>46105</v>
+      </c>
+      <c r="G126" s="46" t="s">
         <v>585</v>
       </c>
-      <c r="H126" s="58" t="s">
-        <v>586</v>
-      </c>
-      <c r="I126" s="58" t="s">
-        <v>587</v>
+      <c r="H126" s="46" t="s">
+        <v>606</v>
+      </c>
+      <c r="I126" s="46" t="s">
+        <v>626</v>
       </c>
       <c r="J126" s="36" t="s">
         <v>76</v>
@@ -9364,7 +9358,7 @@
         <v>76</v>
       </c>
       <c r="O126" s="36" t="s">
-        <v>625</v>
+        <v>563</v>
       </c>
       <c r="P126" s="36" t="s">
         <v>76</v>
@@ -9376,7 +9370,7 @@
         <v>76</v>
       </c>
       <c r="S126" s="36" t="s">
-        <v>633</v>
+        <v>571</v>
       </c>
       <c r="T126" s="36"/>
       <c r="U126" s="36"/>
@@ -9401,17 +9395,17 @@
       <c r="E127" s="41" t="s">
         <v>269</v>
       </c>
-      <c r="F127" s="57">
-        <v>46093</v>
-      </c>
-      <c r="G127" s="58" t="s">
-        <v>588</v>
-      </c>
-      <c r="H127" s="58" t="s">
-        <v>589</v>
-      </c>
-      <c r="I127" s="58" t="s">
-        <v>590</v>
+      <c r="F127" s="45">
+        <v>46105</v>
+      </c>
+      <c r="G127" s="46" t="s">
+        <v>586</v>
+      </c>
+      <c r="H127" s="46" t="s">
+        <v>607</v>
+      </c>
+      <c r="I127" s="46" t="s">
+        <v>627</v>
       </c>
       <c r="J127" s="36" t="s">
         <v>76</v>
@@ -9425,7 +9419,7 @@
         <v>76</v>
       </c>
       <c r="O127" s="36" t="s">
-        <v>626</v>
+        <v>564</v>
       </c>
       <c r="P127" s="36" t="s">
         <v>76</v>
@@ -9437,7 +9431,7 @@
         <v>76</v>
       </c>
       <c r="S127" s="36" t="s">
-        <v>633</v>
+        <v>571</v>
       </c>
       <c r="T127" s="36"/>
       <c r="U127" s="36"/>
@@ -9462,17 +9456,17 @@
       <c r="E128" s="41" t="s">
         <v>271</v>
       </c>
-      <c r="F128" s="57">
-        <v>46093</v>
-      </c>
-      <c r="G128" s="58" t="s">
-        <v>591</v>
-      </c>
-      <c r="H128" s="58" t="s">
-        <v>592</v>
-      </c>
-      <c r="I128" s="58" t="s">
-        <v>593</v>
+      <c r="F128" s="45">
+        <v>46105</v>
+      </c>
+      <c r="G128" s="46" t="s">
+        <v>587</v>
+      </c>
+      <c r="H128" s="46" t="s">
+        <v>608</v>
+      </c>
+      <c r="I128" s="46" t="s">
+        <v>628</v>
       </c>
       <c r="J128" s="36" t="s">
         <v>76</v>
@@ -9486,7 +9480,7 @@
         <v>76</v>
       </c>
       <c r="O128" s="36" t="s">
-        <v>627</v>
+        <v>565</v>
       </c>
       <c r="P128" s="36" t="s">
         <v>76</v>
@@ -9498,7 +9492,7 @@
         <v>76</v>
       </c>
       <c r="S128" s="36" t="s">
-        <v>633</v>
+        <v>571</v>
       </c>
       <c r="T128" s="36"/>
       <c r="U128" s="36"/>
@@ -9523,17 +9517,17 @@
       <c r="E129" s="41" t="s">
         <v>273</v>
       </c>
-      <c r="F129" s="57">
-        <v>46093</v>
-      </c>
-      <c r="G129" s="58" t="s">
-        <v>594</v>
-      </c>
-      <c r="H129" s="58" t="s">
-        <v>595</v>
-      </c>
-      <c r="I129" s="58" t="s">
-        <v>596</v>
+      <c r="F129" s="45">
+        <v>46105</v>
+      </c>
+      <c r="G129" s="46" t="s">
+        <v>588</v>
+      </c>
+      <c r="H129" s="46" t="s">
+        <v>609</v>
+      </c>
+      <c r="I129" s="46" t="s">
+        <v>629</v>
       </c>
       <c r="J129" s="36" t="s">
         <v>76</v>
@@ -9547,7 +9541,7 @@
         <v>76</v>
       </c>
       <c r="O129" s="36" t="s">
-        <v>628</v>
+        <v>566</v>
       </c>
       <c r="P129" s="36" t="s">
         <v>76</v>
@@ -9559,7 +9553,7 @@
         <v>76</v>
       </c>
       <c r="S129" s="36" t="s">
-        <v>633</v>
+        <v>571</v>
       </c>
       <c r="T129" s="36"/>
       <c r="U129" s="36"/>
@@ -9584,17 +9578,17 @@
       <c r="E130" s="41" t="s">
         <v>275</v>
       </c>
-      <c r="F130" s="57">
-        <v>46093</v>
-      </c>
-      <c r="G130" s="58" t="s">
-        <v>597</v>
-      </c>
-      <c r="H130" s="58" t="s">
-        <v>598</v>
-      </c>
-      <c r="I130" s="58" t="s">
-        <v>599</v>
+      <c r="F130" s="45">
+        <v>46105</v>
+      </c>
+      <c r="G130" s="46" t="s">
+        <v>589</v>
+      </c>
+      <c r="H130" s="46" t="s">
+        <v>610</v>
+      </c>
+      <c r="I130" s="46" t="s">
+        <v>630</v>
       </c>
       <c r="J130" s="36" t="s">
         <v>76</v>
@@ -9608,7 +9602,7 @@
         <v>76</v>
       </c>
       <c r="O130" s="36" t="s">
-        <v>629</v>
+        <v>567</v>
       </c>
       <c r="P130" s="36" t="s">
         <v>76</v>
@@ -9620,7 +9614,7 @@
         <v>76</v>
       </c>
       <c r="S130" s="36" t="s">
-        <v>633</v>
+        <v>571</v>
       </c>
       <c r="T130" s="36"/>
       <c r="U130" s="36"/>
@@ -10868,17 +10862,17 @@
       <c r="E164" s="41" t="s">
         <v>342</v>
       </c>
-      <c r="F164" s="57">
-        <v>46093</v>
-      </c>
-      <c r="G164" s="58" t="s">
-        <v>600</v>
-      </c>
-      <c r="H164" s="58" t="s">
-        <v>601</v>
-      </c>
-      <c r="I164" s="58" t="s">
-        <v>602</v>
+      <c r="F164" s="45">
+        <v>46105</v>
+      </c>
+      <c r="G164" s="46" t="s">
+        <v>590</v>
+      </c>
+      <c r="H164" s="46" t="s">
+        <v>611</v>
+      </c>
+      <c r="I164" s="46" t="s">
+        <v>631</v>
       </c>
       <c r="J164" s="36" t="s">
         <v>76</v>
@@ -10915,10 +10909,10 @@
       <c r="E165" s="41" t="s">
         <v>344</v>
       </c>
-      <c r="F165" s="57"/>
-      <c r="G165" s="58"/>
-      <c r="H165" s="58"/>
-      <c r="I165" s="58"/>
+      <c r="F165" s="45"/>
+      <c r="G165" s="46"/>
+      <c r="H165" s="46"/>
+      <c r="I165" s="46"/>
       <c r="J165" s="36" t="s">
         <v>543</v>
       </c>
@@ -10926,7 +10920,7 @@
         <v>506</v>
       </c>
       <c r="L165" s="36" t="s">
-        <v>634</v>
+        <v>572</v>
       </c>
       <c r="M165" s="36"/>
       <c r="N165" s="36"/>
@@ -11328,17 +11322,17 @@
       <c r="E176" s="41" t="s">
         <v>366</v>
       </c>
-      <c r="F176" s="57">
-        <v>46093</v>
-      </c>
-      <c r="G176" s="58" t="s">
-        <v>603</v>
-      </c>
-      <c r="H176" s="58" t="s">
-        <v>604</v>
-      </c>
-      <c r="I176" s="58" t="s">
-        <v>605</v>
+      <c r="F176" s="45">
+        <v>46105</v>
+      </c>
+      <c r="G176" s="46" t="s">
+        <v>591</v>
+      </c>
+      <c r="H176" s="46" t="s">
+        <v>612</v>
+      </c>
+      <c r="I176" s="46" t="s">
+        <v>632</v>
       </c>
       <c r="J176" s="36" t="s">
         <v>76</v>
@@ -11352,7 +11346,7 @@
         <v>76</v>
       </c>
       <c r="O176" s="36" t="s">
-        <v>630</v>
+        <v>568</v>
       </c>
       <c r="P176" s="36" t="s">
         <v>76</v>
@@ -11364,7 +11358,7 @@
         <v>76</v>
       </c>
       <c r="S176" s="36" t="s">
-        <v>633</v>
+        <v>571</v>
       </c>
       <c r="T176" s="36"/>
       <c r="U176" s="33"/>
@@ -11611,17 +11605,17 @@
       <c r="E183" s="41" t="s">
         <v>380</v>
       </c>
-      <c r="F183" s="57">
-        <v>46093</v>
-      </c>
-      <c r="G183" s="58" t="s">
-        <v>606</v>
-      </c>
-      <c r="H183" s="58" t="s">
-        <v>607</v>
-      </c>
-      <c r="I183" s="58" t="s">
-        <v>608</v>
+      <c r="F183" s="45">
+        <v>46105</v>
+      </c>
+      <c r="G183" s="46" t="s">
+        <v>592</v>
+      </c>
+      <c r="H183" s="46" t="s">
+        <v>613</v>
+      </c>
+      <c r="I183" s="46" t="s">
+        <v>633</v>
       </c>
       <c r="J183" s="36" t="s">
         <v>76</v>
@@ -11635,7 +11629,7 @@
         <v>76</v>
       </c>
       <c r="O183" s="36" t="s">
-        <v>631</v>
+        <v>569</v>
       </c>
       <c r="P183" s="36" t="s">
         <v>76</v>
@@ -11647,7 +11641,7 @@
         <v>76</v>
       </c>
       <c r="S183" s="36" t="s">
-        <v>633</v>
+        <v>571</v>
       </c>
       <c r="T183" s="36"/>
       <c r="U183" s="33"/>
@@ -11894,17 +11888,17 @@
       <c r="E190" s="41" t="s">
         <v>394</v>
       </c>
-      <c r="F190" s="61">
-        <v>46093</v>
-      </c>
-      <c r="G190" s="62" t="s">
-        <v>609</v>
-      </c>
-      <c r="H190" s="62" t="s">
-        <v>610</v>
-      </c>
-      <c r="I190" s="62" t="s">
-        <v>611</v>
+      <c r="F190" s="45">
+        <v>46105</v>
+      </c>
+      <c r="G190" s="46" t="s">
+        <v>593</v>
+      </c>
+      <c r="H190" s="46" t="s">
+        <v>614</v>
+      </c>
+      <c r="I190" s="46" t="s">
+        <v>634</v>
       </c>
       <c r="J190" s="36" t="s">
         <v>76</v>
@@ -11917,8 +11911,8 @@
       <c r="N190" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="O190" s="63" t="s">
-        <v>632</v>
+      <c r="O190" s="36" t="s">
+        <v>570</v>
       </c>
       <c r="P190" s="36" t="s">
         <v>76</v>
@@ -11929,11 +11923,11 @@
       <c r="R190" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="S190" s="63" t="s">
-        <v>633</v>
+      <c r="S190" s="49" t="s">
+        <v>571</v>
       </c>
       <c r="T190" s="36"/>
-      <c r="U190" s="63"/>
+      <c r="U190" s="49"/>
       <c r="V190" s="38"/>
       <c r="W190" s="36" t="s">
         <v>50</v>
@@ -16977,8 +16971,8 @@
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="portrait"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
